--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_np_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_np_control_chart_testcases.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -326,7 +326,7 @@
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="K4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L4" t="inlineStr" s="2">
@@ -496,7 +496,7 @@
       </c>
       <c r="K5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L5" t="inlineStr" s="2">
@@ -586,7 +586,7 @@
       </c>
       <c r="K6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L6" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-变量区域基础交互</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-变量区域基础交互</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -930,7 +930,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-变量区域基础交互</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-变量区域基础交互</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-变量区域基础交互</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-变量区域基础交互</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-变量区域基础交互</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-变量区域基础交互</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="2">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="K14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="2">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图、coverage_dimension_rules.md-小数位数默认选项</t>
+          <t xml:space="preserve">来源：prd、UI图、coverage_dimension_rules.md-小数位数默认选项</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-未分析首次进入字段匹配</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-未分析首次进入字段匹配</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-未分析首次进入字段匹配</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-未分析首次进入字段匹配</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-分析结果名称</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-分析结果名称</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程、coverage_dimension_rules.md-数据源预览</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md、coverage_dimension_rules.md-数据源预览</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-PNG/JPG导出</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-PNG/JPG导出</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图、coverage_dimension_rules.md-分析图标题</t>
+          <t xml:space="preserve">来源：prd、UI图、coverage_dimension_rules.md-分析图标题</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-分析结果名称</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-分析结果名称</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程、coverage_dimension_rules.md-多变量缺失拆分覆盖</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、coverage_dimension_rules.md-多变量缺失拆分覆盖</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、UI图、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_np_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_np_control_chart_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -331,7 +331,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -358,7 +358,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -528,17 +528,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -618,17 +618,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -704,17 +704,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -790,17 +790,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -876,17 +876,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -935,7 +935,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -962,17 +962,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1049,17 +1049,17 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1136,17 +1136,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1222,17 +1222,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1308,17 +1308,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1393,17 +1393,17 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1479,17 +1479,17 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1566,17 +1566,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1653,17 +1653,17 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1739,17 +1739,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1825,17 +1825,17 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -1911,17 +1911,17 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -1997,17 +1997,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2083,17 +2083,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2169,17 +2169,17 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2256,17 +2256,17 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2341,12 +2341,12 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
@@ -2433,17 +2433,17 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -2517,17 +2517,17 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2691,17 +2691,17 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -2776,17 +2776,17 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -2865,12 +2865,12 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -2954,12 +2954,12 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
@@ -3040,12 +3040,12 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
@@ -3127,17 +3127,17 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
@@ -3213,12 +3213,12 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3299,17 +3299,17 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3384,17 +3384,17 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3469,17 +3469,17 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
@@ -3554,12 +3554,12 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -3644,12 +3644,12 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
@@ -3731,17 +3731,17 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -3818,17 +3818,17 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -3905,12 +3905,12 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
@@ -3991,17 +3991,17 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -4078,17 +4078,17 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -4164,17 +4164,17 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -4250,12 +4250,12 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
@@ -4337,17 +4337,17 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -4424,17 +4424,17 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
@@ -4511,17 +4511,17 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
@@ -4598,17 +4598,17 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="2">
@@ -4685,7 +4685,7 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -4773,17 +4773,17 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置后分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
@@ -4858,7 +4858,7 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -4945,12 +4945,12 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
@@ -5031,17 +5031,17 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析结果提示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -5117,17 +5117,17 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析结果提示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="2">
@@ -5204,12 +5204,12 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
@@ -5292,17 +5292,17 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
@@ -5381,12 +5381,12 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
@@ -5468,12 +5468,12 @@
     <row r="63" ht="64" customHeight="1">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
@@ -5555,17 +5555,17 @@
     <row r="64" ht="64" customHeight="1">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
@@ -5641,17 +5641,17 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="2">
@@ -5727,17 +5727,17 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="2">
@@ -5813,12 +5813,12 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
@@ -5903,12 +5903,12 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
@@ -5993,17 +5993,17 @@
     <row r="69" ht="64" customHeight="1">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="2">
@@ -6082,17 +6082,17 @@
     <row r="70" ht="64" customHeight="1">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="2">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -6341,7 +6341,7 @@
     <row r="73" ht="64" customHeight="1">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
